--- a/QuantStudio/Resource/BaoStockDBInfo.xlsx
+++ b/QuantStudio/Resource/BaoStockDBInfo.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>TableName</t>
   </si>
@@ -71,7 +71,19 @@
     <t>A股</t>
   </si>
   <si>
-    <t>http://baostock.com/baostock/index.php/A%E8%82%A1K%E7%BA%BF%E6%95%B0%E6%8D%AE</t>
+    <t>http://baostock.com/mainContent?file=stockKData.md</t>
+  </si>
+  <si>
+    <t>行业分类</t>
+  </si>
+  <si>
+    <t>query_stock_industry</t>
+  </si>
+  <si>
+    <t>DTTable</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=stockIndustry.md</t>
   </si>
   <si>
     <t>FieldName</t>
@@ -212,6 +224,30 @@
     <t>是否ST股，1是，0否</t>
   </si>
   <si>
+    <t>updateDate</t>
+  </si>
+  <si>
+    <t>更新日期</t>
+  </si>
+  <si>
+    <t>code_name</t>
+  </si>
+  <si>
+    <t>证券名称</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>所属行业</t>
+  </si>
+  <si>
+    <t>industryClassification</t>
+  </si>
+  <si>
+    <t>所属行业类别</t>
+  </si>
+  <si>
     <t>ArgName</t>
   </si>
   <si>
@@ -270,6 +306,9 @@
   </si>
   <si>
     <t>{"arg_type": "SingleOption","option_range":["1","2","3"]}</t>
+  </si>
+  <si>
+    <t>2026-01-18</t>
   </si>
 </sst>
 </file>
@@ -282,10 +321,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -753,140 +800,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1235,15 +1283,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="29.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="35.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
     <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="16.6583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6583333333333" customWidth="1"/>
+    <col min="4" max="4" width="39" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1289,12 +1338,33 @@
         <v>12</v>
       </c>
     </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F2" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="http://baostock.com/baostock/index.php/A%E8%82%A1K%E7%BA%BF%E6%95%B0%E6%8D%AE" tooltip="http://baostock.com/baostock/index.php/A%E8%82%A1K%E7%BA%BF%E6%95%B0%E6%8D%AE"/>
+    <hyperlink ref="G2" r:id="rId1" display="http://baostock.com/mainContent?file=stockKData.md" tooltip="http://baostock.com/mainContent?file=stockKData.md"/>
+    <hyperlink ref="G3" r:id="rId2" display="http://baostock.com/mainContent?file=stockIndustry.md"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1305,15 +1375,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.8333333333333" customWidth="1"/>
     <col min="2" max="2" width="29.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="14.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:6">
@@ -1321,16 +1391,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -1341,16 +1411,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1358,16 +1428,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1375,16 +1445,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1392,16 +1462,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1409,16 +1479,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1426,16 +1496,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1443,16 +1513,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1460,16 +1530,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1477,16 +1547,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1494,16 +1564,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1511,16 +1581,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1528,16 +1598,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1545,16 +1615,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1562,16 +1632,16 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1579,16 +1649,16 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1596,16 +1666,16 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1613,16 +1683,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1630,16 +1700,101 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
         <v>26</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>27</v>
       </c>
-      <c r="F19" t="s">
-        <v>58</v>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1655,8 +1810,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="18.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
@@ -1672,19 +1827,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1695,16 +1850,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1712,16 +1867,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1729,16 +1884,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1746,16 +1901,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1763,19 +1918,19 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1783,19 +1938,53 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" t="s">
-        <v>78</v>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
